--- a/root_domains_AIHealthcare_Partials.xlsx
+++ b/root_domains_AIHealthcare_Partials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Oxford\Master Thesis\Data for DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DB0AE0E-7E45-4E44-9B78-B6DFF122A2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199EF036-1146-4D40-A211-A9569A48E0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C4EA7231-3DFA-4BB0-86FB-92DE812873A8}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{C4EA7231-3DFA-4BB0-86FB-92DE812873A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>ey.com/de_de</t>
   </si>
   <si>
-    <t>domains</t>
+    <t>domain</t>
   </si>
 </sst>
 </file>
